--- a/camera_kit.xlsx
+++ b/camera_kit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\camera_kits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DF7CF6-006F-4848-BD06-BE75C302E773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1256ED76-C1CC-4510-B75B-CED7242CBB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30816" yWindow="-96" windowWidth="30912" windowHeight="16752" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>Item</t>
   </si>
@@ -119,7 +119,28 @@
     <t>拼多多。二手并不便宜。第一个镜头优先探索焦段需求，暂缓考虑画质</t>
   </si>
   <si>
-    <t>补充夜景</t>
+    <t>也太重了！</t>
+  </si>
+  <si>
+    <t>也太重了！而且是2021年的</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>SD卡</t>
+  </si>
+  <si>
+    <t>索尼</t>
+  </si>
+  <si>
+    <t>二手1700。新的3300</t>
+  </si>
+  <si>
+    <t>补充夜景。想买个好的。也没打算买更贵的35。二手3000左右。新的3600</t>
+  </si>
+  <si>
+    <t>128G</t>
   </si>
 </sst>
 </file>
@@ -128,7 +149,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -198,32 +219,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Komma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="25">
     <dxf>
       <font>
         <b val="0"/>
@@ -259,7 +280,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
     <dxf>
       <font>
@@ -278,7 +299,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
     <dxf>
       <font>
@@ -315,7 +336,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
     <dxf>
       <font>
@@ -388,7 +409,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -407,121 +427,116 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
     <dxf>
       <font>
@@ -580,6 +595,48 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -609,26 +666,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}" name="Tabell1" displayName="Tabell1" ref="A1:J13" totalsRowCount="1" headerRowDxfId="12" dataDxfId="10" totalsRowDxfId="11">
-  <autoFilter ref="A1:J12" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J12">
-    <sortCondition ref="B1:B12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}" name="Tabell1" displayName="Tabell1" ref="A1:K16" totalsRowCount="1" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+  <autoFilter ref="A1:K15" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K15">
+    <sortCondition ref="B1:B15"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F96E38C4-EE51-47B2-8465-83D716E7CD86}" name="Item" dataDxfId="22" totalsRowDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{290B4921-101D-4EC3-9BA1-72D2EE653077}" name="焦距 mm" dataDxfId="21" totalsRowDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{CAD9269C-2D02-4EEB-96CE-D8D67E629307}" name="光圈" dataDxfId="20" totalsRowDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{CD3928A2-7D3B-42FF-8165-D81DFAA90150}" name="重量 g" dataDxfId="19" totalsRowDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{9993376C-30BF-47B2-8496-1B7D76B01E7D}" name="直径 mm" dataDxfId="18" totalsRowDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{8BF984FB-FE14-461C-B7B8-271BAF39CF27}" name="Price CNY" dataDxfId="17" totalsRowDxfId="4" dataCellStyle="Komma"/>
-    <tableColumn id="7" xr3:uid="{254F7275-9C66-4096-9CA9-A474E7A7FA27}" name="Buy" dataDxfId="16" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{C562AE0D-0297-468F-B857-0C7E741F4CAF}" name="Budget" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="2" dataCellStyle="Komma">
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{F96E38C4-EE51-47B2-8465-83D716E7CD86}" name="Item" dataDxfId="21" totalsRowDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{290B4921-101D-4EC3-9BA1-72D2EE653077}" name="焦距 mm" dataDxfId="20" totalsRowDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{CAD9269C-2D02-4EEB-96CE-D8D67E629307}" name="光圈" dataDxfId="19" totalsRowDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{CD3928A2-7D3B-42FF-8165-D81DFAA90150}" name="重量 g" dataDxfId="18" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{9993376C-30BF-47B2-8496-1B7D76B01E7D}" name="直径 mm" dataDxfId="17" totalsRowDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{7F550482-A657-4C51-BECA-FD7AD22A173C}" name="Year" dataDxfId="11" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{8BF984FB-FE14-461C-B7B8-271BAF39CF27}" name="Price CNY" dataDxfId="16" totalsRowDxfId="4" dataCellStyle="Komma"/>
+    <tableColumn id="7" xr3:uid="{254F7275-9C66-4096-9CA9-A474E7A7FA27}" name="Buy" dataDxfId="15" totalsRowDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{C562AE0D-0297-468F-B857-0C7E741F4CAF}" name="Budget" totalsRowFunction="sum" dataDxfId="14" totalsRowDxfId="2" dataCellStyle="Komma">
       <calculatedColumnFormula>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{60048395-27AC-49C9-A0CE-E9BBDB4150EF}" name="Carried" totalsRowFunction="sum" dataDxfId="14" totalsRowDxfId="1" dataCellStyle="Komma">
+    <tableColumn id="10" xr3:uid="{60048395-27AC-49C9-A0CE-E9BBDB4150EF}" name="Carried" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="1" dataCellStyle="Komma">
       <calculatedColumnFormula>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{22514279-C08A-4A21-8911-E2CF7BD669F0}" name="Notes" dataDxfId="13" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{22514279-C08A-4A21-8911-E2CF7BD669F0}" name="Notes" dataDxfId="12" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -897,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -905,15 +963,16 @@
     <col min="3" max="3" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="69.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="73.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -929,23 +988,26 @@
       <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
@@ -961,313 +1023,434 @@
       <c r="E2" s="5">
         <v>62</v>
       </c>
-      <c r="F2" s="8">
-        <v>3600</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="F2" s="5">
+        <v>2025</v>
+      </c>
+      <c r="G2" s="8">
+        <v>3000</v>
+      </c>
+      <c r="H2" s="5">
         <v>1</v>
       </c>
-      <c r="H2" s="8">
+      <c r="I2" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>3600</v>
-      </c>
-      <c r="I2" s="8">
+        <v>3000</v>
+      </c>
+      <c r="J2" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>490</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K2" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B3" s="6">
         <v>35</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5">
+        <v>645</v>
+      </c>
+      <c r="E3" s="5">
+        <v>67</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2021</v>
+      </c>
+      <c r="G3" s="8">
+        <v>4700</v>
+      </c>
+      <c r="I3" s="8">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="8">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6">
+        <v>35</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D4" s="5">
         <v>426</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E4" s="5">
         <v>62</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F4" s="5">
+        <v>2025</v>
+      </c>
+      <c r="G4" s="8">
         <v>1550</v>
       </c>
-      <c r="H3" s="8">
+      <c r="I4" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>0</v>
       </c>
-      <c r="I3" s="8">
+      <c r="J4" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+    <row r="5" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B5" s="10">
         <v>50</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D5" s="9">
         <v>421</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E5" s="9">
         <v>62</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F5" s="9">
+        <v>2023</v>
+      </c>
+      <c r="G5" s="12">
         <v>1000</v>
       </c>
-      <c r="G4" s="9">
+      <c r="I5" s="12">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="10">
+        <v>50</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="9">
+        <v>273</v>
+      </c>
+      <c r="E6" s="9">
+        <v>58</v>
+      </c>
+      <c r="F6" s="9">
+        <v>2025</v>
+      </c>
+      <c r="G6" s="12">
+        <v>800</v>
+      </c>
+      <c r="I6" s="12">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="10">
+        <v>55</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="9">
+        <v>281</v>
+      </c>
+      <c r="E7" s="9">
+        <v>49</v>
+      </c>
+      <c r="F7" s="9">
+        <v>2013</v>
+      </c>
+      <c r="G7" s="12">
+        <v>1700</v>
+      </c>
+      <c r="H7" s="9">
         <v>1</v>
       </c>
-      <c r="H4" s="12">
+      <c r="I7" s="12">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>1700</v>
+      </c>
+      <c r="J7" s="12">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>281</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="10">
+        <v>50</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="9">
+        <v>205</v>
+      </c>
+      <c r="E8" s="9">
+        <v>58</v>
+      </c>
+      <c r="F8" s="9">
+        <v>2025</v>
+      </c>
+      <c r="G8" s="12">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="12">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="14">
+        <v>85</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="13">
+        <v>340</v>
+      </c>
+      <c r="E9" s="13">
+        <v>58</v>
+      </c>
+      <c r="F9" s="13">
+        <v>2025</v>
+      </c>
+      <c r="G9" s="16">
+        <v>1300</v>
+      </c>
+      <c r="H9" s="13">
+        <v>1</v>
+      </c>
+      <c r="I9" s="16">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>1300</v>
+      </c>
+      <c r="J9" s="16">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="14">
+        <v>85</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="13">
+        <v>440</v>
+      </c>
+      <c r="E10" s="13">
+        <v>62</v>
+      </c>
+      <c r="F10" s="13">
+        <v>2024</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1500</v>
+      </c>
+      <c r="I10" s="16">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="16">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1">
+        <v>540</v>
+      </c>
+      <c r="E11" s="1">
+        <v>72</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G11" s="4">
+        <v>4800</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>4800</v>
+      </c>
+      <c r="J11" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>540</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="1">
+        <v>514</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G12" s="4">
+        <v>9500</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>9500</v>
+      </c>
+      <c r="J12" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>514</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>100</v>
+      </c>
+      <c r="J13" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="G14" s="4">
+        <v>200</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>200</v>
+      </c>
+      <c r="J14" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="G15" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>1000</v>
       </c>
-      <c r="I4" s="12">
+      <c r="J15" s="4">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>421</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="10">
-        <v>50</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="9">
-        <v>273</v>
-      </c>
-      <c r="E5" s="9">
-        <v>58</v>
-      </c>
-      <c r="F5" s="12">
-        <v>800</v>
-      </c>
-      <c r="H5" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="10">
-        <v>50</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="9">
-        <v>205</v>
-      </c>
-      <c r="E6" s="9">
-        <v>58</v>
-      </c>
-      <c r="F6" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H6" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="14">
-        <v>85</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="13">
-        <v>340</v>
-      </c>
-      <c r="E7" s="13">
-        <v>58</v>
-      </c>
-      <c r="F7" s="16">
-        <v>1300</v>
-      </c>
-      <c r="G7" s="13">
-        <v>1</v>
-      </c>
-      <c r="H7" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>1300</v>
-      </c>
-      <c r="I7" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="14">
-        <v>85</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="13">
-        <v>440</v>
-      </c>
-      <c r="E8" s="13">
-        <v>62</v>
-      </c>
-      <c r="F8" s="16">
-        <v>1500</v>
-      </c>
-      <c r="H8" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="1">
-        <v>540</v>
-      </c>
-      <c r="E9" s="1">
-        <v>72</v>
-      </c>
-      <c r="F9" s="4">
-        <v>4800</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>4800</v>
-      </c>
-      <c r="I9" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>540</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="1">
-        <v>514</v>
-      </c>
-      <c r="F10" s="4">
-        <v>9500</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>9500</v>
-      </c>
-      <c r="I10" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>514</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="F11" s="4">
-        <v>100</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>100</v>
-      </c>
-      <c r="I11" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="F12" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>1000</v>
-      </c>
-      <c r="I12" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F13" s="17"/>
-      <c r="H13" s="17">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G16" s="17"/>
+      <c r="I16" s="17">
         <f>SUBTOTAL(109,Tabell1[Budget])</f>
-        <v>21300</v>
-      </c>
-      <c r="I13" s="17">
+        <v>21600</v>
+      </c>
+      <c r="J16" s="17">
         <f>SUBTOTAL(109,Tabell1[Carried])</f>
-        <v>2305</v>
+        <v>2165</v>
       </c>
     </row>
   </sheetData>

--- a/camera_kit.xlsx
+++ b/camera_kit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\camera_kits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1256ED76-C1CC-4510-B75B-CED7242CBB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7CC6B2-01F0-491D-B88B-9227804ED6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
   <si>
     <t>Item</t>
   </si>
@@ -137,10 +137,16 @@
     <t>二手1700。新的3300</t>
   </si>
   <si>
-    <t>补充夜景。想买个好的。也没打算买更贵的35。二手3000左右。新的3600</t>
-  </si>
-  <si>
-    <t>128G</t>
+    <t>二手。新的3900</t>
+  </si>
+  <si>
+    <t>二手3000左右。新的3600。偏重。二手比较贵</t>
+  </si>
+  <si>
+    <t>二手。新的3500</t>
+  </si>
+  <si>
+    <t>128G，约2000张Raw+Jpg。</t>
   </si>
 </sst>
 </file>
@@ -449,6 +455,79 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -464,79 +543,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
     <dxf>
       <font>
@@ -666,10 +672,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}" name="Tabell1" displayName="Tabell1" ref="A1:K16" totalsRowCount="1" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:K15" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K15">
-    <sortCondition ref="B1:B15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}" name="Tabell1" displayName="Tabell1" ref="A1:K18" totalsRowCount="1" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+  <autoFilter ref="A1:K17" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
+    <sortCondition ref="B1:B17"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{F96E38C4-EE51-47B2-8465-83D716E7CD86}" name="Item" dataDxfId="21" totalsRowDxfId="10"/>
@@ -677,16 +683,16 @@
     <tableColumn id="11" xr3:uid="{CAD9269C-2D02-4EEB-96CE-D8D67E629307}" name="光圈" dataDxfId="19" totalsRowDxfId="8"/>
     <tableColumn id="6" xr3:uid="{CD3928A2-7D3B-42FF-8165-D81DFAA90150}" name="重量 g" dataDxfId="18" totalsRowDxfId="7"/>
     <tableColumn id="4" xr3:uid="{9993376C-30BF-47B2-8496-1B7D76B01E7D}" name="直径 mm" dataDxfId="17" totalsRowDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{7F550482-A657-4C51-BECA-FD7AD22A173C}" name="Year" dataDxfId="11" totalsRowDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{8BF984FB-FE14-461C-B7B8-271BAF39CF27}" name="Price CNY" dataDxfId="16" totalsRowDxfId="4" dataCellStyle="Komma"/>
-    <tableColumn id="7" xr3:uid="{254F7275-9C66-4096-9CA9-A474E7A7FA27}" name="Buy" dataDxfId="15" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{C562AE0D-0297-468F-B857-0C7E741F4CAF}" name="Budget" totalsRowFunction="sum" dataDxfId="14" totalsRowDxfId="2" dataCellStyle="Komma">
+    <tableColumn id="9" xr3:uid="{7F550482-A657-4C51-BECA-FD7AD22A173C}" name="Year" dataDxfId="16" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{8BF984FB-FE14-461C-B7B8-271BAF39CF27}" name="Price CNY" dataDxfId="15" totalsRowDxfId="4" dataCellStyle="Komma"/>
+    <tableColumn id="7" xr3:uid="{254F7275-9C66-4096-9CA9-A474E7A7FA27}" name="Buy" dataDxfId="14" totalsRowDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{C562AE0D-0297-468F-B857-0C7E741F4CAF}" name="Budget" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="2" dataCellStyle="Komma">
       <calculatedColumnFormula>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{60048395-27AC-49C9-A0CE-E9BBDB4150EF}" name="Carried" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="1" dataCellStyle="Komma">
+    <tableColumn id="10" xr3:uid="{60048395-27AC-49C9-A0CE-E9BBDB4150EF}" name="Carried" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="1" dataCellStyle="Komma">
       <calculatedColumnFormula>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{22514279-C08A-4A21-8911-E2CF7BD669F0}" name="Notes" dataDxfId="12" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{22514279-C08A-4A21-8911-E2CF7BD669F0}" name="Notes" dataDxfId="11" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -955,7 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1009,16 +1015,16 @@
     </row>
     <row r="2" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B2" s="6">
         <v>35</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="5">
-        <v>490</v>
+        <v>426</v>
       </c>
       <c r="E2" s="5">
         <v>62</v>
@@ -1027,26 +1033,20 @@
         <v>2025</v>
       </c>
       <c r="G2" s="8">
-        <v>3000</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1</v>
+        <v>1550</v>
       </c>
       <c r="I2" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J2" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>490</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="6">
         <v>35</v>
@@ -1055,32 +1055,35 @@
         <v>17</v>
       </c>
       <c r="D3" s="5">
-        <v>645</v>
+        <v>490</v>
       </c>
       <c r="E3" s="5">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F3" s="5">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="G3" s="8">
-        <v>4700</v>
+        <v>3000</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
       </c>
       <c r="I3" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J3" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B4" s="6">
         <v>35</v>
@@ -1089,16 +1092,16 @@
         <v>18</v>
       </c>
       <c r="D4" s="5">
-        <v>426</v>
+        <v>280</v>
       </c>
       <c r="E4" s="5">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F4" s="5">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="G4" s="8">
-        <v>1550</v>
+        <v>2500</v>
       </c>
       <c r="I4" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
@@ -1108,44 +1111,47 @@
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="10">
-        <v>50</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="9">
-        <v>421</v>
-      </c>
-      <c r="E5" s="9">
-        <v>62</v>
-      </c>
-      <c r="F5" s="9">
-        <v>2023</v>
-      </c>
-      <c r="G5" s="12">
-        <v>1000</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="K4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="6">
+        <v>35</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5">
+        <v>645</v>
+      </c>
+      <c r="E5" s="5">
+        <v>67</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2021</v>
+      </c>
+      <c r="G5" s="8">
+        <v>4700</v>
+      </c>
+      <c r="I5" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>0</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="8">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
-      <c r="K5" s="9" t="s">
-        <v>27</v>
+      <c r="K5" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B6" s="10">
         <v>50</v>
@@ -1154,16 +1160,16 @@
         <v>18</v>
       </c>
       <c r="D6" s="9">
-        <v>273</v>
+        <v>421</v>
       </c>
       <c r="E6" s="9">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F6" s="9">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="G6" s="12">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="I6" s="12">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
@@ -1173,56 +1179,53 @@
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
+      <c r="K6" s="9" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B7" s="10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" s="9">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="E7" s="9">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F7" s="9">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="G7" s="12">
-        <v>1700</v>
-      </c>
-      <c r="H7" s="9">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="I7" s="12">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J7" s="12">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>281</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="10">
         <v>50</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="9">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="E8" s="9">
         <v>58</v>
@@ -1231,7 +1234,7 @@
         <v>2025</v>
       </c>
       <c r="G8" s="12">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="I8" s="12">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
@@ -1242,38 +1245,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="14">
-        <v>85</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="13">
-        <v>340</v>
-      </c>
-      <c r="E9" s="13">
-        <v>58</v>
-      </c>
-      <c r="F9" s="13">
-        <v>2025</v>
-      </c>
-      <c r="G9" s="16">
-        <v>1300</v>
-      </c>
-      <c r="H9" s="13">
+    <row r="9" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="10">
+        <v>55</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="9">
+        <v>281</v>
+      </c>
+      <c r="E9" s="9">
+        <v>49</v>
+      </c>
+      <c r="F9" s="9">
+        <v>2013</v>
+      </c>
+      <c r="G9" s="12">
+        <v>1700</v>
+      </c>
+      <c r="H9" s="9">
         <v>1</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="12">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>1300</v>
-      </c>
-      <c r="J9" s="16">
+        <v>1700</v>
+      </c>
+      <c r="J9" s="12">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>340</v>
+        <v>281</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -1307,93 +1313,109 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="14">
+        <v>85</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="13">
+        <v>340</v>
+      </c>
+      <c r="E11" s="13">
+        <v>58</v>
+      </c>
+      <c r="F11" s="13">
+        <v>2025</v>
+      </c>
+      <c r="G11" s="16">
+        <v>1300</v>
+      </c>
+      <c r="H11" s="13">
+        <v>1</v>
+      </c>
+      <c r="I11" s="16">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>1300</v>
+      </c>
+      <c r="J11" s="16">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="14">
+        <v>85</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="13">
+        <v>371</v>
+      </c>
+      <c r="E12" s="13">
+        <v>67</v>
+      </c>
+      <c r="F12" s="13">
+        <v>2017</v>
+      </c>
+      <c r="G12" s="16">
+        <v>2000</v>
+      </c>
+      <c r="I12" s="16">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="16">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D13" s="1">
         <v>540</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E13" s="1">
         <v>72</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F13" s="1">
         <v>2025</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G13" s="4">
         <v>4800</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H13" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I13" s="4">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>4800</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J13" s="4">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>540</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="1">
-        <v>514</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G12" s="4">
-        <v>9500</v>
-      </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="I12" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>9500</v>
-      </c>
-      <c r="J12" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>514</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="G13" s="4">
-        <v>100</v>
-      </c>
-      <c r="H13" s="1">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>100</v>
-      </c>
-      <c r="J13" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1416,39 +1438,91 @@
         <v>0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15" s="3"/>
+      <c r="D15" s="1">
+        <v>514</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2023</v>
+      </c>
       <c r="G15" s="4">
-        <v>1000</v>
+        <v>9500</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
       </c>
       <c r="I15" s="4">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>1000</v>
+        <v>9500</v>
       </c>
       <c r="J15" s="4">
         <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="G16" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>1000</v>
+      </c>
+      <c r="J16" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G16" s="17"/>
-      <c r="I16" s="17">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="G17" s="4">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>100</v>
+      </c>
+      <c r="J17" s="4">
+        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G18" s="17"/>
+      <c r="I18" s="17">
         <f>SUBTOTAL(109,Tabell1[Budget])</f>
         <v>21600</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J18" s="17">
         <f>SUBTOTAL(109,Tabell1[Carried])</f>
         <v>2165</v>
       </c>

--- a/camera_kit.xlsx
+++ b/camera_kit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\camera_kits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7CC6B2-01F0-491D-B88B-9227804ED6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE20053-05FE-4D60-9D80-508708EF49F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
   <si>
     <t>Item</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Sony A7C2</t>
   </si>
   <si>
-    <t>转转二手。国行新品11000</t>
-  </si>
-  <si>
     <t>配件</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
     <t>直径 mm</t>
   </si>
   <si>
-    <t>Buy</t>
-  </si>
-  <si>
     <t>Budget</t>
   </si>
   <si>
@@ -122,9 +116,6 @@
     <t>也太重了！</t>
   </si>
   <si>
-    <t>也太重了！而且是2021年的</t>
-  </si>
-  <si>
     <t>Year</t>
   </si>
   <si>
@@ -134,19 +125,37 @@
     <t>索尼</t>
   </si>
   <si>
-    <t>二手1700。新的3300</t>
-  </si>
-  <si>
     <t>二手。新的3900</t>
   </si>
   <si>
     <t>二手3000左右。新的3600。偏重。二手比较贵</t>
   </si>
   <si>
-    <t>二手。新的3500</t>
-  </si>
-  <si>
     <t>128G，约2000张Raw+Jpg。</t>
+  </si>
+  <si>
+    <t>二手。新的3500。据说性能不如唯卓仕</t>
+  </si>
+  <si>
+    <t>新的3000。太重。据说性能一般</t>
+  </si>
+  <si>
+    <t>二手1700。新的3300。过于老旧</t>
+  </si>
+  <si>
+    <t>也太重了！而且是2021年的。二手。新的4800</t>
+  </si>
+  <si>
+    <t>转转二手也要9700+</t>
+  </si>
+  <si>
+    <t>看看能否等到55Evo</t>
+  </si>
+  <si>
+    <t>Røde 麦克风</t>
+  </si>
+  <si>
+    <t>Bought</t>
   </si>
 </sst>
 </file>
@@ -218,7 +227,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -245,12 +254,13 @@
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Komma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -455,6 +465,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -499,7 +519,11 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -672,27 +696,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}" name="Tabell1" displayName="Tabell1" ref="A1:K18" totalsRowCount="1" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:K17" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
-    <sortCondition ref="B1:B17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}" name="Tabell1" displayName="Tabell1" ref="A1:K20" totalsRowCount="1" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="23">
+  <autoFilter ref="A1:K19" xr:uid="{4B44A64F-1F32-4A13-9687-9F9344E00A77}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K19">
+    <sortCondition ref="B1:B19"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F96E38C4-EE51-47B2-8465-83D716E7CD86}" name="Item" dataDxfId="21" totalsRowDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{290B4921-101D-4EC3-9BA1-72D2EE653077}" name="焦距 mm" dataDxfId="20" totalsRowDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{CAD9269C-2D02-4EEB-96CE-D8D67E629307}" name="光圈" dataDxfId="19" totalsRowDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{CD3928A2-7D3B-42FF-8165-D81DFAA90150}" name="重量 g" dataDxfId="18" totalsRowDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{9993376C-30BF-47B2-8496-1B7D76B01E7D}" name="直径 mm" dataDxfId="17" totalsRowDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{7F550482-A657-4C51-BECA-FD7AD22A173C}" name="Year" dataDxfId="16" totalsRowDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{8BF984FB-FE14-461C-B7B8-271BAF39CF27}" name="Price CNY" dataDxfId="15" totalsRowDxfId="4" dataCellStyle="Komma"/>
-    <tableColumn id="7" xr3:uid="{254F7275-9C66-4096-9CA9-A474E7A7FA27}" name="Buy" dataDxfId="14" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{C562AE0D-0297-468F-B857-0C7E741F4CAF}" name="Budget" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="2" dataCellStyle="Komma">
-      <calculatedColumnFormula>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{F96E38C4-EE51-47B2-8465-83D716E7CD86}" name="Item" dataDxfId="22" totalsRowDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{290B4921-101D-4EC3-9BA1-72D2EE653077}" name="焦距 mm" dataDxfId="21" totalsRowDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{CAD9269C-2D02-4EEB-96CE-D8D67E629307}" name="光圈" dataDxfId="20" totalsRowDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{CD3928A2-7D3B-42FF-8165-D81DFAA90150}" name="重量 g" dataDxfId="19" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{9993376C-30BF-47B2-8496-1B7D76B01E7D}" name="直径 mm" dataDxfId="18" totalsRowDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{7F550482-A657-4C51-BECA-FD7AD22A173C}" name="Year" dataDxfId="17" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{8BF984FB-FE14-461C-B7B8-271BAF39CF27}" name="Price CNY" dataDxfId="16" totalsRowDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{A33E6C2B-E1CF-4897-9523-3B24579B0A39}" name="Bought" dataDxfId="15" totalsRowDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{C562AE0D-0297-468F-B857-0C7E741F4CAF}" name="Budget" totalsRowFunction="sum" dataDxfId="14" totalsRowDxfId="2">
+      <calculatedColumnFormula>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{60048395-27AC-49C9-A0CE-E9BBDB4150EF}" name="Carried" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="1" dataCellStyle="Komma">
-      <calculatedColumnFormula>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{60048395-27AC-49C9-A0CE-E9BBDB4150EF}" name="Carried" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="1">
+      <calculatedColumnFormula>#REF!*Tabell1[[#This Row],[重量 g]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{22514279-C08A-4A21-8911-E2CF7BD669F0}" name="Notes" dataDxfId="11" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{22514279-C08A-4A21-8911-E2CF7BD669F0}" name="Notes" dataDxfId="12" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -961,20 +985,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="73.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="69.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -983,31 +1007,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>2</v>
@@ -1015,13 +1039,13 @@
     </row>
     <row r="2" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="6">
         <v>35</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" s="5">
         <v>426</v>
@@ -1036,23 +1060,23 @@
         <v>1550</v>
       </c>
       <c r="I2" s="8">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>0</v>
       </c>
       <c r="J2" s="8">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" s="6">
         <v>35</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" s="5">
         <v>490</v>
@@ -1066,30 +1090,27 @@
       <c r="G3" s="8">
         <v>3000</v>
       </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
       <c r="I3" s="8">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>3000</v>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
       </c>
       <c r="J3" s="8">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>490</v>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="6">
         <v>35</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5">
         <v>280</v>
@@ -1104,26 +1125,26 @@
         <v>2500</v>
       </c>
       <c r="I4" s="8">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>0</v>
       </c>
       <c r="J4" s="8">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="6">
         <v>35</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5">
         <v>645</v>
@@ -1135,29 +1156,29 @@
         <v>2021</v>
       </c>
       <c r="G5" s="8">
-        <v>4700</v>
+        <v>3600</v>
       </c>
       <c r="I5" s="8">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>0</v>
       </c>
       <c r="J5" s="8">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="10">
         <v>50</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" s="9">
         <v>421</v>
@@ -1172,26 +1193,26 @@
         <v>1000</v>
       </c>
       <c r="I6" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>0</v>
       </c>
       <c r="J6" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" s="10">
         <v>50</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" s="9">
         <v>205</v>
@@ -1206,23 +1227,26 @@
         <v>1000</v>
       </c>
       <c r="I7" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>0</v>
       </c>
       <c r="J7" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="10">
         <v>50</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" s="9">
         <v>273</v>
@@ -1237,23 +1261,23 @@
         <v>800</v>
       </c>
       <c r="I8" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>0</v>
       </c>
       <c r="J8" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B9" s="10">
         <v>55</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="9">
         <v>281</v>
@@ -1267,30 +1291,27 @@
       <c r="G9" s="12">
         <v>1700</v>
       </c>
-      <c r="H9" s="9">
-        <v>1</v>
-      </c>
       <c r="I9" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>1700</v>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
       </c>
       <c r="J9" s="12">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>281</v>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="14">
         <v>85</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" s="13">
         <v>440</v>
@@ -1305,23 +1326,23 @@
         <v>1500</v>
       </c>
       <c r="I10" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>0</v>
       </c>
       <c r="J10" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="14">
         <v>85</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" s="13">
         <v>340</v>
@@ -1339,195 +1360,251 @@
         <v>1</v>
       </c>
       <c r="I11" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
         <v>1300</v>
       </c>
       <c r="J11" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B12" s="14">
         <v>85</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D12" s="13">
-        <v>371</v>
+        <v>540</v>
       </c>
       <c r="E12" s="13">
         <v>67</v>
       </c>
       <c r="F12" s="13">
+        <v>2024</v>
+      </c>
+      <c r="G12" s="16">
+        <v>1600</v>
+      </c>
+      <c r="I12" s="16">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="16">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="14">
+        <v>85</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="13">
+        <v>371</v>
+      </c>
+      <c r="E13" s="13">
+        <v>67</v>
+      </c>
+      <c r="F13" s="13">
         <v>2017</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G13" s="16">
         <v>2000</v>
       </c>
-      <c r="I12" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="16">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1">
-        <v>540</v>
-      </c>
-      <c r="E13" s="1">
-        <v>72</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G13" s="4">
-        <v>4800</v>
-      </c>
-      <c r="H13" s="1">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>4800</v>
-      </c>
-      <c r="J13" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>540</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>26</v>
+      <c r="I13" s="16">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="16">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1">
+        <v>540</v>
+      </c>
+      <c r="E14" s="1">
+        <v>72</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2025</v>
+      </c>
       <c r="G14" s="4">
-        <v>200</v>
+        <v>4600</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>200</v>
-      </c>
-      <c r="J14" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>4600</v>
+      </c>
+      <c r="J14" s="18">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>540</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="1">
-        <v>514</v>
-      </c>
       <c r="F15" s="1">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G15" s="4">
-        <v>9500</v>
-      </c>
-      <c r="H15" s="1">
-        <v>1</v>
+        <v>575</v>
       </c>
       <c r="I15" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>9500</v>
-      </c>
-      <c r="J15" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>514</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>4</v>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="18">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3"/>
       <c r="G16" s="4">
-        <v>1000</v>
+        <v>369</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
-        <v>1000</v>
-      </c>
-      <c r="J16" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>369</v>
+      </c>
+      <c r="J16" s="18">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
         <v>0</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3"/>
+      <c r="D17" s="1">
+        <v>514</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2023</v>
+      </c>
       <c r="G17" s="4">
-        <v>100</v>
+        <v>9900</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
       </c>
       <c r="I17" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>9900</v>
+      </c>
+      <c r="J17" s="18">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>514</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="G18" s="4">
+        <v>300</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>300</v>
+      </c>
+      <c r="J18" s="18">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="G19" s="4">
         <v>100</v>
       </c>
-      <c r="J17" s="4">
-        <f>Tabell1[[#This Row],[Buy]]*Tabell1[[#This Row],[重量 g]]</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G18" s="17"/>
-      <c r="I18" s="17">
+      <c r="I19" s="4">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[Price CNY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="18">
+        <f>Tabell1[[#This Row],[Bought]]*Tabell1[[#This Row],[重量 g]]</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G20" s="17"/>
+      <c r="I20" s="17">
         <f>SUBTOTAL(109,Tabell1[Budget])</f>
-        <v>21600</v>
-      </c>
-      <c r="J18" s="17">
+        <v>16469</v>
+      </c>
+      <c r="J20" s="17">
         <f>SUBTOTAL(109,Tabell1[Carried])</f>
-        <v>2165</v>
+        <v>1394</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
